--- a/Templates/fedramp-moderate-template-ssp.xlsx
+++ b/Templates/fedramp-moderate-template-ssp.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>The system enforces account management through an identity governance platform. All user accounts require manager approval before provisioning. Accounts are reviewed quarterly and disabled after 90 days of inactivity. Service accounts are inventoried and rotated on schedule.</t>
+          <t>The system enforces account management through AWS IAM. All user accounts require manager approval before provisioning. Accounts are reviewed quarterly and disabled after 90 days of inactivity. Service accounts are inventoried and rotated on schedule.</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>The system logs all authentication events, authorization decisions, administrative actions, data access events, and system events. Logs are forwarded to a centralized SIEM. Log retention meets the minimum 90-day active and 1-year archive requirement.</t>
+          <t>The system logs all authentication events, authorization decisions, and administrative actions through AWS CloudTrail. Logs are forwarded to a centralized SIEM. Log retention meets the minimum 12-month requirement with 90 days immediately available.</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>All changes to production require a change request ticket with justification, security impact analysis, and approval. Changes are tested in staging before production. Emergency changes follow an expedited process with post-implementation review.</t>
+          <t>All changes to production are managed through GitHub with branch protection and required pull request reviews. Changes are tested in staging before production. Emergency changes follow an expedited approval with post-implementation review.</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Vulnerability scans are performed continuously against all system components. Critical vulnerabilities remediated within 15 days, high within 30 days. Scan results correlated with asset inventory for complete coverage.</t>
+          <t>Vulnerability scans are performed continuously using Prowler for cloud security posture and Trivy for container and dependency scanning. Critical vulnerabilities remediated within 15 days, high within 30 days. Scan results correlated with asset inventory for coverage validation.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>All data at rest is encrypted using AES-256 managed through the key management service. Encryption is enforced at the storage layer. Unencrypted storage resources are flagged as non-compliant.</t>
+          <t>All data at rest is encrypted using AES-256 through AWS S3 server-side encryption and AWS KMS for key management. Encryption is enforced at the storage layer. Unencrypted storage resources are flagged as non-compliant.</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Continuous monitoring through SIEM integration. Network traffic analysis detects anomalous patterns. Security operations reviews alerts daily. Critical alerts trigger automated incident creation.</t>
+          <t>Continuous monitoring through AWS CloudWatch and VPC Flow Logs. Network traffic analysis detects anomalous patterns. Security operations reviews alerts daily. Critical alerts trigger automated incident creation.</t>
         </is>
       </c>
     </row>
